--- a/reports/module-migration-sunset-backlog/2026-07-27/LEGACY_PATH_AND_CONSUMER_SUNSET_REGISTER.xlsx
+++ b/reports/module-migration-sunset-backlog/2026-07-27/LEGACY_PATH_AND_CONSUMER_SUNSET_REGISTER.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sunset Register" sheetId="1" r:id="Rbf1a917fd04a43d4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sunset Register" sheetId="1" r:id="R5147ac9a13bb4bfb"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -425,10 +425,10 @@
         <x:v>May write different structured_data shapes than golden-bar path</x:v>
       </x:c>
       <x:c r="G3" s="5" t="str">
-        <x:v>Both generation engines emit one typed artifact contract into one lifecycle</x:v>
+        <x:v>Retain deliverable_runs as operations.job_run or equivalent durable generation ledger; migrate/link generated_artifacts into the common deliverable lifecycle and make it non-authoritative after parity</x:v>
       </x:c>
       <x:c r="H3" s="5" t="str">
-        <x:v>ACTIVE -&gt; DUAL_RUN -&gt; NEW_READ_PRIMARY -&gt; LEGACY_READ_ONLY -&gt; ARCHIVED -&gt; DROPPED</x:v>
+        <x:v>deliverable_runs: RETAIN_OPERATIONAL; generated_artifacts: ACTIVE -&gt; DUAL_RUN -&gt; NEW_READ_PRIMARY -&gt; LEGACY_READ_ONLY -&gt; ARCHIVED -&gt; DROPPED</x:v>
       </x:c>
       <x:c r="I3" s="5" t="str">
         <x:v>moves.deliverable_signed_off; moves.gate_approved; moves.program_published</x:v>
@@ -437,10 +437,10 @@
         <x:v>60 days after typed contract parity</x:v>
       </x:c>
       <x:c r="K3" s="5" t="str">
-        <x:v>Retain run evidence and model/prompt lineage as audit history</x:v>
+        <x:v>Retain run evidence and model/prompt lineage as audit history; only generated_artifacts authority may be archived after parity and retention gates</x:v>
       </x:c>
       <x:c r="L3" s="5" t="str">
-        <x:v>Explicit later approval after historical artifact backfill</x:v>
+        <x:v>No drop of durable run ledger authorized; generated_artifacts retirement requires explicit later approval after historical artifact backfill</x:v>
       </x:c>
       <x:c r="M3" s="5" t="str">
         <x:v>path_level_candidate</x:v>
